--- a/data/trans_orig/P6604-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6604-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a posiciones dolorosas/ fatigantes en su trabajo en 2007</t>
+          <t>Población según la exposición a posiciones dolorosas/ fatigantes en su trabajo en 2007 (tasa de respuesta: 99,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76927</t>
+          <t>76124</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>109494</t>
+          <t>108649</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41112</t>
+          <t>40947</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64506</t>
+          <t>64651</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>125660</t>
+          <t>125123</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>164523</t>
+          <t>166867</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66501</t>
+          <t>65126</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100185</t>
+          <t>97281</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23165</t>
+          <t>22898</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43277</t>
+          <t>42080</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94939</t>
+          <t>94166</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>132308</t>
+          <t>132148</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89010</t>
+          <t>89120</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>124177</t>
+          <t>123718</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25449</t>
+          <t>24842</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46756</t>
+          <t>46099</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>122207</t>
+          <t>119302</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>161873</t>
+          <t>162972</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,87%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80525</t>
+          <t>79613</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>113467</t>
+          <t>115395</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22844</t>
+          <t>22930</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43940</t>
+          <t>43005</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>111045</t>
+          <t>109569</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>149902</t>
+          <t>152360</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>284150</t>
+          <t>282241</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>346488</t>
+          <t>345125</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>245031</t>
+          <t>244247</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>293492</t>
+          <t>291043</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>547652</t>
+          <t>545075</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>629119</t>
+          <t>624954</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,67%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>262921</t>
+          <t>265000</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>320488</t>
+          <t>324409</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>131649</t>
+          <t>131778</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>175854</t>
+          <t>176027</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>408969</t>
+          <t>408394</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>484880</t>
+          <t>481519</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,25%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>270760</t>
+          <t>268906</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>328139</t>
+          <t>327036</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83756</t>
+          <t>83132</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122669</t>
+          <t>121582</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>357826</t>
+          <t>367705</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>429870</t>
+          <t>437225</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,66%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>191369</t>
+          <t>191275</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>244592</t>
+          <t>244296</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46682</t>
+          <t>46815</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>76450</t>
+          <t>76739</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>248217</t>
+          <t>245889</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>311584</t>
+          <t>308247</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>213970</t>
+          <t>215462</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>255002</t>
+          <t>257628</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>178125</t>
+          <t>177778</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>210928</t>
+          <t>210363</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>404386</t>
+          <t>403025</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>458226</t>
+          <t>456684</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>65,66%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>87143</t>
+          <t>85999</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>124151</t>
+          <t>123017</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>48272</t>
+          <t>49565</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>78100</t>
+          <t>77957</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>142474</t>
+          <t>145783</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>189036</t>
+          <t>191738</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29282</t>
+          <t>29506</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53127</t>
+          <t>54495</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14700</t>
+          <t>13623</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32384</t>
+          <t>31509</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>48476</t>
+          <t>46689</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>77661</t>
+          <t>78049</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15571</t>
+          <t>16166</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36017</t>
+          <t>36776</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6822</t>
+          <t>6991</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21456</t>
+          <t>23351</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25820</t>
+          <t>26648</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51157</t>
+          <t>51656</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>600557</t>
+          <t>602254</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>690631</t>
+          <t>688464</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>481078</t>
+          <t>483932</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>545069</t>
+          <t>547522</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1109667</t>
+          <t>1107108</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1218523</t>
+          <t>1216345</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,55%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>439205</t>
+          <t>441566</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>519056</t>
+          <t>518544</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>219701</t>
+          <t>222249</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>275125</t>
+          <t>280601</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>677476</t>
+          <t>674026</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>772576</t>
+          <t>770085</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,3%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>404107</t>
+          <t>406469</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>479676</t>
+          <t>481169</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>134253</t>
+          <t>135537</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>181528</t>
+          <t>179670</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>557155</t>
+          <t>554188</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>645972</t>
+          <t>642956</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>303552</t>
+          <t>305309</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>374229</t>
+          <t>377636</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>86435</t>
+          <t>85746</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>125350</t>
+          <t>127083</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>401560</t>
+          <t>405199</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>485815</t>
+          <t>487862</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a posiciones dolorosas/ fatigantes en su trabajo en 2012</t>
+          <t>Población según la exposición a posiciones dolorosas/ fatigantes en su trabajo en 2012 (tasa de respuesta: 99,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23660</t>
+          <t>24038</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44295</t>
+          <t>43634</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33388</t>
+          <t>33724</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55691</t>
+          <t>56217</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63678</t>
+          <t>61613</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95519</t>
+          <t>93562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44219</t>
+          <t>44772</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69384</t>
+          <t>69848</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44664</t>
+          <t>44973</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68143</t>
+          <t>68191</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>95329</t>
+          <t>95806</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>130834</t>
+          <t>129639</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,01%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49258</t>
+          <t>48802</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>76777</t>
+          <t>74437</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14763</t>
+          <t>14785</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32048</t>
+          <t>32503</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>67369</t>
+          <t>69907</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>100682</t>
+          <t>100385</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24232</t>
+          <t>24467</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46356</t>
+          <t>44487</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10401</t>
+          <t>11325</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27724</t>
+          <t>26673</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39418</t>
+          <t>39096</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66829</t>
+          <t>66655</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,57%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>225014</t>
+          <t>225689</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>281170</t>
+          <t>279988</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>171601</t>
+          <t>169832</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>217549</t>
+          <t>215553</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>407561</t>
+          <t>405498</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>479861</t>
+          <t>482723</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,58%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>290914</t>
+          <t>288669</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>344185</t>
+          <t>345869</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>177073</t>
+          <t>175075</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>220220</t>
+          <t>223082</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>474555</t>
+          <t>480616</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>553212</t>
+          <t>556275</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,55%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>203559</t>
+          <t>203848</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>255692</t>
+          <t>254185</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>103696</t>
+          <t>105300</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145383</t>
+          <t>144804</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>321536</t>
+          <t>316773</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>387595</t>
+          <t>389652</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,3%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92714</t>
+          <t>92039</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>135266</t>
+          <t>134544</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42589</t>
+          <t>41323</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71963</t>
+          <t>71832</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>143560</t>
+          <t>144092</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>194508</t>
+          <t>192451</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>145529</t>
+          <t>148635</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>182728</t>
+          <t>187433</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>93306</t>
+          <t>92189</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>125621</t>
+          <t>124641</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>251811</t>
+          <t>250571</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>300515</t>
+          <t>298796</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,39%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>70056</t>
+          <t>67519</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>103675</t>
+          <t>102152</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>69269</t>
+          <t>67213</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>100261</t>
+          <t>100562</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>145796</t>
+          <t>145909</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>191078</t>
+          <t>190731</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,72%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38244</t>
+          <t>39094</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67929</t>
+          <t>68818</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17144</t>
+          <t>17008</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38459</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61321</t>
+          <t>61098</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97468</t>
+          <t>98538</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7970</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22486</t>
+          <t>21433</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>7798</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21783</t>
+          <t>21695</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17673</t>
+          <t>17539</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38682</t>
+          <t>38118</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>415248</t>
+          <t>416182</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>489152</t>
+          <t>486711</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>317257</t>
+          <t>318267</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>377268</t>
+          <t>377903</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>751498</t>
+          <t>748183</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>845036</t>
+          <t>846469</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,95%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>426311</t>
+          <t>421937</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>494138</t>
+          <t>494611</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>306910</t>
+          <t>308564</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>369426</t>
+          <t>368949</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>748392</t>
+          <t>749807</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>843394</t>
+          <t>845901</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,92%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>310844</t>
+          <t>311861</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>376015</t>
+          <t>377223</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>147253</t>
+          <t>149646</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>200080</t>
+          <t>198651</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>472828</t>
+          <t>475819</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>554790</t>
+          <t>566036</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>24,04%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>136579</t>
+          <t>135806</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>183952</t>
+          <t>185881</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>70801</t>
+          <t>72253</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>106140</t>
+          <t>106417</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>218024</t>
+          <t>216153</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>279303</t>
+          <t>279020</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a posiciones dolorosas/ fatigantes en su trabajo en 2016</t>
+          <t>Población según la exposición a posiciones dolorosas/ fatigantes en su trabajo en 2016 (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13833</t>
+          <t>13399</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31875</t>
+          <t>31865</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13810</t>
+          <t>13105</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28255</t>
+          <t>28046</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30233</t>
+          <t>30388</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52553</t>
+          <t>54061</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27928</t>
+          <t>28542</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50059</t>
+          <t>49066</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11177</t>
+          <t>11250</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26246</t>
+          <t>26468</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43818</t>
+          <t>44494</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69362</t>
+          <t>70744</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,51%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31325</t>
+          <t>31883</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54383</t>
+          <t>53161</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13800</t>
+          <t>13497</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28701</t>
+          <t>28612</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>50113</t>
+          <t>48899</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>75289</t>
+          <t>75705</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,86%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26382</t>
+          <t>27587</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49741</t>
+          <t>49963</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>8189</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22106</t>
+          <t>21224</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39526</t>
+          <t>39313</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64898</t>
+          <t>64252</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,44%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>219342</t>
+          <t>220391</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>274577</t>
+          <t>275212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>193681</t>
+          <t>194535</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>239922</t>
+          <t>241568</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>429389</t>
+          <t>427468</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>503023</t>
+          <t>495553</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,52%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>273504</t>
+          <t>268374</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>332175</t>
+          <t>330636</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>190430</t>
+          <t>191336</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>238919</t>
+          <t>239797</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>479089</t>
+          <t>478445</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>554636</t>
+          <t>555338</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,32%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>212750</t>
+          <t>216504</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>269064</t>
+          <t>273109</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>122433</t>
+          <t>124088</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>167954</t>
+          <t>166989</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>347319</t>
+          <t>353481</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>418222</t>
+          <t>422023</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,84%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>109626</t>
+          <t>112605</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>156629</t>
+          <t>158247</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>60232</t>
+          <t>60755</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>92804</t>
+          <t>93274</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>182503</t>
+          <t>181613</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>236653</t>
+          <t>237605</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>151964</t>
+          <t>153933</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>193212</t>
+          <t>193603</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>138309</t>
+          <t>138432</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>174657</t>
+          <t>174296</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>300579</t>
+          <t>303175</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>355874</t>
+          <t>355398</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,15%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>98577</t>
+          <t>100859</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>137024</t>
+          <t>136233</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71339</t>
+          <t>70698</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>102401</t>
+          <t>101478</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>182123</t>
+          <t>181786</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>229924</t>
+          <t>229961</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,04%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28240</t>
+          <t>28427</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52274</t>
+          <t>53340</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34375</t>
+          <t>34319</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59879</t>
+          <t>59263</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68227</t>
+          <t>68421</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102341</t>
+          <t>102942</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10053</t>
+          <t>10059</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25854</t>
+          <t>27136</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13836</t>
+          <t>13655</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32188</t>
+          <t>32643</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27786</t>
+          <t>27870</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51522</t>
+          <t>54263</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>405353</t>
+          <t>407175</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>478989</t>
+          <t>472164</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>359918</t>
+          <t>360828</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>422065</t>
+          <t>423650</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>785156</t>
+          <t>786052</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>880693</t>
+          <t>879785</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,06%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>422455</t>
+          <t>425300</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>496449</t>
+          <t>496809</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>289450</t>
+          <t>287526</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>348276</t>
+          <t>349854</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>730699</t>
+          <t>729661</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>824853</t>
+          <t>823457</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,75%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>290709</t>
+          <t>289488</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>354532</t>
+          <t>350963</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>184230</t>
+          <t>183754</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>236419</t>
+          <t>237805</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>485040</t>
+          <t>490295</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>570092</t>
+          <t>571457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>163310</t>
+          <t>164248</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>217050</t>
+          <t>214728</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>91342</t>
+          <t>91765</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>131878</t>
+          <t>131904</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>269660</t>
+          <t>266029</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>334568</t>
+          <t>334134</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a posiciones dolorosas/ fatigantes en su trabajo en 2023</t>
+          <t>Población según la exposición a posiciones dolorosas/ fatigantes en su trabajo en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>6850</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21709</t>
+          <t>22045</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>11514</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12287</t>
+          <t>11560</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28232</t>
+          <t>27983</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,77%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18613</t>
+          <t>19275</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9674</t>
+          <t>10293</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19166</t>
+          <t>19629</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18103</t>
+          <t>19391</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35003</t>
+          <t>35272</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,74%</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15677</t>
+          <t>15511</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31154</t>
+          <t>32592</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15605</t>
+          <t>15553</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24752</t>
+          <t>25023</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43371</t>
+          <t>44479</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>42,55%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11019</t>
+          <t>11583</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25910</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4080</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13437</t>
+          <t>13490</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17392</t>
+          <t>17700</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34293</t>
+          <t>35029</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>33,51%</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>169595</t>
+          <t>166556</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>615045</t>
+          <t>619856</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>84119</t>
+          <t>84210</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>130323</t>
+          <t>129816</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>275073</t>
+          <t>278705</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>795711</t>
+          <t>857754</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>68,78%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90833</t>
+          <t>89175</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>319822</t>
+          <t>323794</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>114096</t>
+          <t>117465</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>170169</t>
+          <t>172388</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>209268</t>
+          <t>193767</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>470771</t>
+          <t>467715</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,5%</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62364</t>
+          <t>59838</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>215689</t>
+          <t>218386</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75544</t>
+          <t>80174</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>118343</t>
+          <t>118634</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129704</t>
+          <t>109448</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>321725</t>
+          <t>316994</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,42%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32170</t>
+          <t>28788</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>123075</t>
+          <t>119826</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47998</t>
+          <t>49959</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>165473</t>
+          <t>160512</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>87457</t>
+          <t>91403</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>249282</t>
+          <t>252296</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>120718</t>
+          <t>120384</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>153072</t>
+          <t>153105</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>80785</t>
+          <t>81926</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>106729</t>
+          <t>105851</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>210003</t>
+          <t>208998</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>252510</t>
+          <t>251511</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,02%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55196</t>
+          <t>56380</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>83977</t>
+          <t>82514</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>55315</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>78540</t>
+          <t>77936</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>118483</t>
+          <t>116428</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>155134</t>
+          <t>157074</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,61%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11697</t>
+          <t>10921</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30691</t>
+          <t>29415</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17099</t>
+          <t>17778</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36157</t>
+          <t>35251</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32405</t>
+          <t>32825</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59443</t>
+          <t>57322</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>8912</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32398</t>
+          <t>30520</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>7670</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22565</t>
+          <t>20970</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19426</t>
+          <t>19341</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44288</t>
+          <t>43423</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>341613</t>
+          <t>341018</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>804570</t>
+          <t>773344</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>179351</t>
+          <t>174847</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>234186</t>
+          <t>232794</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>545654</t>
+          <t>544027</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1091558</t>
+          <t>1122900</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>62,63%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>153805</t>
+          <t>166276</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>393567</t>
+          <t>389949</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>196215</t>
+          <t>187727</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>255421</t>
+          <t>254768</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>351215</t>
+          <t>337464</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>624859</t>
+          <t>625238</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>99017</t>
+          <t>96607</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>249391</t>
+          <t>250234</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>114464</t>
+          <t>114467</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>157202</t>
+          <t>157517</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>216765</t>
+          <t>206100</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>388661</t>
+          <t>389524</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,73%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>54876</t>
+          <t>59349</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>153734</t>
+          <t>156512</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>69052</t>
+          <t>68074</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>190835</t>
+          <t>234541</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>139063</t>
+          <t>144368</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>302220</t>
+          <t>307670</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6604-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6604-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76124</t>
+          <t>77192</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>108649</t>
+          <t>109461</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40947</t>
+          <t>41136</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64651</t>
+          <t>64519</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>125123</t>
+          <t>124113</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>166867</t>
+          <t>165172</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,28%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65126</t>
+          <t>63964</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>97281</t>
+          <t>98146</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22898</t>
+          <t>22026</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42080</t>
+          <t>42929</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94166</t>
+          <t>93574</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>132148</t>
+          <t>133384</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89120</t>
+          <t>89062</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24842</t>
+          <t>26061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46099</t>
+          <t>46881</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>119302</t>
+          <t>120587</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>162972</t>
+          <t>164403</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>31,14%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79613</t>
+          <t>80230</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>115395</t>
+          <t>115020</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22930</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43005</t>
+          <t>44240</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>109569</t>
+          <t>108545</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>152360</t>
+          <t>152008</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,79%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>282241</t>
+          <t>285873</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>345125</t>
+          <t>349129</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>244247</t>
+          <t>243474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>291043</t>
+          <t>291993</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>545075</t>
+          <t>539783</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>624954</t>
+          <t>621740</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,48%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>265000</t>
+          <t>262821</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>324409</t>
+          <t>321057</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>131778</t>
+          <t>131437</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>176027</t>
+          <t>175142</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>408394</t>
+          <t>407185</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>481519</t>
+          <t>482084</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,29%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>268906</t>
+          <t>270427</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>327036</t>
+          <t>328863</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83132</t>
+          <t>82776</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>121582</t>
+          <t>119329</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>367705</t>
+          <t>364509</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>437225</t>
+          <t>433772</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>191275</t>
+          <t>190616</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>244296</t>
+          <t>246126</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46815</t>
+          <t>45323</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>76739</t>
+          <t>76282</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>245889</t>
+          <t>246374</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>308247</t>
+          <t>310684</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>215462</t>
+          <t>215050</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>257628</t>
+          <t>254904</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>177778</t>
+          <t>177063</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>210363</t>
+          <t>209804</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>403025</t>
+          <t>404770</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>456684</t>
+          <t>456663</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85999</t>
+          <t>89825</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>123017</t>
+          <t>124024</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>49565</t>
+          <t>48585</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>77957</t>
+          <t>77281</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>145783</t>
+          <t>146174</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>191738</t>
+          <t>192010</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,61%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29506</t>
+          <t>29120</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54495</t>
+          <t>55225</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13623</t>
+          <t>13858</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31509</t>
+          <t>33428</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46689</t>
+          <t>48074</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78049</t>
+          <t>78973</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16166</t>
+          <t>16432</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36776</t>
+          <t>36266</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6991</t>
+          <t>6387</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23351</t>
+          <t>21112</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26648</t>
+          <t>25975</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51656</t>
+          <t>51579</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>602254</t>
+          <t>602828</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>688464</t>
+          <t>683821</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>483932</t>
+          <t>481205</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>547522</t>
+          <t>546429</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1107108</t>
+          <t>1107970</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1216345</t>
+          <t>1210341</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,34%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>441566</t>
+          <t>438626</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>518544</t>
+          <t>516804</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>222249</t>
+          <t>218595</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>280601</t>
+          <t>274512</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>674026</t>
+          <t>676440</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>770085</t>
+          <t>769372</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>406469</t>
+          <t>406485</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>481169</t>
+          <t>484731</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>135537</t>
+          <t>135152</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>179670</t>
+          <t>183117</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>554188</t>
+          <t>558690</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>642956</t>
+          <t>648174</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>305309</t>
+          <t>302615</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>377636</t>
+          <t>372817</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>85746</t>
+          <t>85399</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>127083</t>
+          <t>127055</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>405199</t>
+          <t>402619</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>487862</t>
+          <t>481466</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24038</t>
+          <t>23457</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43634</t>
+          <t>44143</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33724</t>
+          <t>34148</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56217</t>
+          <t>56765</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61613</t>
+          <t>62355</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93562</t>
+          <t>92393</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,52%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44772</t>
+          <t>44187</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69848</t>
+          <t>69652</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44973</t>
+          <t>44123</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68191</t>
+          <t>67646</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>95806</t>
+          <t>95537</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>129639</t>
+          <t>129950</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,11%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48802</t>
+          <t>47950</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>74437</t>
+          <t>73698</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14785</t>
+          <t>14888</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32503</t>
+          <t>32886</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>69907</t>
+          <t>69405</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>100385</t>
+          <t>100774</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,1%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24467</t>
+          <t>24166</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44487</t>
+          <t>46450</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11325</t>
+          <t>10450</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26673</t>
+          <t>27597</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39096</t>
+          <t>39017</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66655</t>
+          <t>66620</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>225689</t>
+          <t>224835</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>279988</t>
+          <t>282519</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>169832</t>
+          <t>173203</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>215553</t>
+          <t>220079</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>405498</t>
+          <t>407164</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>482723</t>
+          <t>479577</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,37%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>288669</t>
+          <t>289196</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>345869</t>
+          <t>349461</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>175075</t>
+          <t>173410</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>223082</t>
+          <t>219911</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>480616</t>
+          <t>482399</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>556275</t>
+          <t>551960</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,26%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>203848</t>
+          <t>205248</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>254185</t>
+          <t>255889</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>105300</t>
+          <t>105909</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>144804</t>
+          <t>148360</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>316773</t>
+          <t>319113</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>389652</t>
+          <t>386623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92039</t>
+          <t>93379</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>134544</t>
+          <t>136285</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41323</t>
+          <t>42731</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71832</t>
+          <t>70516</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>144092</t>
+          <t>143446</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>192451</t>
+          <t>193025</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>148635</t>
+          <t>145244</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>187433</t>
+          <t>185369</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>92189</t>
+          <t>94278</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>124641</t>
+          <t>126774</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>250571</t>
+          <t>249693</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>298796</t>
+          <t>298937</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,42%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>67519</t>
+          <t>67649</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>102152</t>
+          <t>100547</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>67213</t>
+          <t>68067</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>100562</t>
+          <t>99923</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>145909</t>
+          <t>146028</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>190731</t>
+          <t>193155</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>35,16%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39094</t>
+          <t>39144</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68818</t>
+          <t>67314</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17008</t>
+          <t>15549</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38459</t>
+          <t>36462</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61098</t>
+          <t>61385</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98538</t>
+          <t>97260</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>7920</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21433</t>
+          <t>23419</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7798</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21695</t>
+          <t>22066</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17539</t>
+          <t>17799</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38118</t>
+          <t>38068</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>416182</t>
+          <t>414746</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>486711</t>
+          <t>491301</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>318267</t>
+          <t>318039</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>377903</t>
+          <t>375279</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>748183</t>
+          <t>747880</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>846469</t>
+          <t>844555</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,87%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>421937</t>
+          <t>424588</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>494611</t>
+          <t>496895</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>308564</t>
+          <t>305791</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>368949</t>
+          <t>366016</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>749807</t>
+          <t>746431</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>845901</t>
+          <t>845699</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,91%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>311861</t>
+          <t>308229</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>377223</t>
+          <t>376425</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>149646</t>
+          <t>148817</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>198651</t>
+          <t>197880</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>475819</t>
+          <t>472132</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>566036</t>
+          <t>556280</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>135806</t>
+          <t>138331</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>185881</t>
+          <t>187284</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>72253</t>
+          <t>68687</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>106417</t>
+          <t>104952</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>216153</t>
+          <t>217085</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>279020</t>
+          <t>281416</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13399</t>
+          <t>13369</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31865</t>
+          <t>31349</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13105</t>
+          <t>13830</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28046</t>
+          <t>28513</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30388</t>
+          <t>30491</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54061</t>
+          <t>54766</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,94%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28542</t>
+          <t>28537</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49066</t>
+          <t>50190</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11250</t>
+          <t>11146</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26468</t>
+          <t>25817</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44494</t>
+          <t>44335</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70744</t>
+          <t>70679</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,48%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31883</t>
+          <t>30929</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53161</t>
+          <t>53333</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>13457</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28612</t>
+          <t>27905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>48899</t>
+          <t>48936</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>75705</t>
+          <t>76398</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>36,19%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27587</t>
+          <t>27314</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49963</t>
+          <t>49721</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>7587</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21224</t>
+          <t>21719</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39313</t>
+          <t>39734</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64252</t>
+          <t>67118</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>31,8%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>220391</t>
+          <t>218425</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>275212</t>
+          <t>277381</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>194535</t>
+          <t>190547</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>241568</t>
+          <t>240161</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>427468</t>
+          <t>428386</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>495553</t>
+          <t>501568</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>268374</t>
+          <t>272839</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>330636</t>
+          <t>332118</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>191336</t>
+          <t>194101</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>239797</t>
+          <t>239974</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>478445</t>
+          <t>479684</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>555338</t>
+          <t>555913</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,36%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>216504</t>
+          <t>211020</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>273109</t>
+          <t>266595</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>124088</t>
+          <t>124359</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166989</t>
+          <t>165537</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>353481</t>
+          <t>347227</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>422023</t>
+          <t>419876</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,7%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>112605</t>
+          <t>112731</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>158247</t>
+          <t>156499</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>60755</t>
+          <t>60058</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>93274</t>
+          <t>93141</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>181613</t>
+          <t>180236</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>237605</t>
+          <t>234842</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,94%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>153933</t>
+          <t>154468</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>193603</t>
+          <t>191938</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>138432</t>
+          <t>137885</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>174296</t>
+          <t>173936</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>303175</t>
+          <t>304838</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>355398</t>
+          <t>357727</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,5%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>100859</t>
+          <t>99102</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136233</t>
+          <t>136807</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>70698</t>
+          <t>71956</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>101478</t>
+          <t>102464</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>181786</t>
+          <t>178697</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>229961</t>
+          <t>227705</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,69%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28427</t>
+          <t>29157</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53340</t>
+          <t>54929</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34319</t>
+          <t>33241</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59263</t>
+          <t>58543</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68421</t>
+          <t>67867</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102942</t>
+          <t>102970</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10059</t>
+          <t>9773</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27136</t>
+          <t>26162</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13655</t>
+          <t>13659</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32643</t>
+          <t>31483</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7279,7 +7279,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27870</t>
+          <t>27315</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54263</t>
+          <t>52200</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>407175</t>
+          <t>405136</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>472164</t>
+          <t>477263</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>360828</t>
+          <t>362975</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>423650</t>
+          <t>424599</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>786052</t>
+          <t>788878</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>879785</t>
+          <t>885893</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,31%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>425300</t>
+          <t>421542</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>496809</t>
+          <t>494798</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>287526</t>
+          <t>290518</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>349854</t>
+          <t>346777</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>729661</t>
+          <t>726844</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>823457</t>
+          <t>822748</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,72%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>289488</t>
+          <t>288723</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>350963</t>
+          <t>353917</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>183754</t>
+          <t>186504</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>237805</t>
+          <t>234393</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>490295</t>
+          <t>489859</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>571457</t>
+          <t>578987</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>164248</t>
+          <t>163850</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>214728</t>
+          <t>214993</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>91765</t>
+          <t>89387</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>131904</t>
+          <t>130776</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>266029</t>
+          <t>262118</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>334134</t>
+          <t>337340</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -8249,32 +8249,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12935</t>
+          <t>13464</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>7413</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22045</t>
+          <t>23175</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8284,32 +8284,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6326</t>
+          <t>6661</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11514</t>
+          <t>11691</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8319,32 +8319,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>19262</t>
+          <t>20125</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11560</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27983</t>
+          <t>31013</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>23,12%</t>
         </is>
       </c>
     </row>
@@ -8362,32 +8362,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11687</t>
+          <t>16138</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>9122</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19275</t>
+          <t>24652</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8397,32 +8397,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14461</t>
+          <t>17263</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10293</t>
+          <t>11927</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19629</t>
+          <t>22906</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8432,32 +8432,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>26148</t>
+          <t>33401</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19391</t>
+          <t>23411</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35272</t>
+          <t>43538</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>32,46%</t>
         </is>
       </c>
     </row>
@@ -8475,32 +8475,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23041</t>
+          <t>29348</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15511</t>
+          <t>19730</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32592</t>
+          <t>39456</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8510,32 +8510,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10539</t>
+          <t>13002</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15553</t>
+          <t>19463</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8545,32 +8545,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>33580</t>
+          <t>42350</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25023</t>
+          <t>30137</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>44479</t>
+          <t>53563</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>39,93%</t>
         </is>
       </c>
     </row>
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17750</t>
+          <t>29003</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11583</t>
+          <t>19496</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>41470</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7797</t>
+          <t>9250</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>5094</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13490</t>
+          <t>15489</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8658,32 +8658,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>25547</t>
+          <t>38253</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17700</t>
+          <t>27337</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35029</t>
+          <t>52380</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>39,05%</t>
         </is>
       </c>
     </row>
@@ -8701,17 +8701,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>87953</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>87953</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>87953</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>46176</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>46176</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>46176</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>104537</t>
+          <t>134129</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>104537</t>
+          <t>134129</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>104537</t>
+          <t>134129</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8818,32 +8818,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>368440</t>
+          <t>139043</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>166556</t>
+          <t>117813</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>619856</t>
+          <t>162505</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8853,32 +8853,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>108979</t>
+          <t>123588</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>84210</t>
+          <t>107118</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>129816</t>
+          <t>143013</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8888,32 +8888,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>477419</t>
+          <t>262632</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>278705</t>
+          <t>235418</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>857754</t>
+          <t>294697</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>27,4%</t>
         </is>
       </c>
     </row>
@@ -8931,32 +8931,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>213589</t>
+          <t>220939</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89175</t>
+          <t>193803</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>323794</t>
+          <t>245561</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8966,32 +8966,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>150042</t>
+          <t>162312</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>117465</t>
+          <t>144219</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>172388</t>
+          <t>183605</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9001,32 +9001,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>363631</t>
+          <t>383251</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>193767</t>
+          <t>350366</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>467715</t>
+          <t>414546</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>38,54%</t>
         </is>
       </c>
     </row>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>145558</t>
+          <t>166917</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59838</t>
+          <t>144210</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>218386</t>
+          <t>192367</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9079,32 +9079,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>100301</t>
+          <t>112290</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>80174</t>
+          <t>95896</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>118634</t>
+          <t>128320</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9114,32 +9114,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>245858</t>
+          <t>279206</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>109448</t>
+          <t>249651</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>316994</t>
+          <t>311275</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>28,94%</t>
         </is>
       </c>
     </row>
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>77776</t>
+          <t>94080</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28788</t>
+          <t>72792</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>119826</t>
+          <t>116269</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>82433</t>
+          <t>56529</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49959</t>
+          <t>44986</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>160512</t>
+          <t>69988</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>160209</t>
+          <t>150609</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>91403</t>
+          <t>127710</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>252296</t>
+          <t>180884</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>805362</t>
+          <t>620979</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>805362</t>
+          <t>620979</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>805362</t>
+          <t>620979</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>441755</t>
+          <t>454719</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>441755</t>
+          <t>454719</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>441755</t>
+          <t>454719</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1247117</t>
+          <t>1075698</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1247117</t>
+          <t>1075698</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1247117</t>
+          <t>1075698</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9387,32 +9387,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>137247</t>
+          <t>156179</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>120384</t>
+          <t>138100</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>153105</t>
+          <t>173802</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9422,32 +9422,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>94226</t>
+          <t>102788</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>81926</t>
+          <t>89143</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>105851</t>
+          <t>115310</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9457,32 +9457,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>231473</t>
+          <t>258967</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>208998</t>
+          <t>238247</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>251511</t>
+          <t>283531</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>58,15%</t>
         </is>
       </c>
     </row>
@@ -9500,32 +9500,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69560</t>
+          <t>73477</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>56380</t>
+          <t>58676</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>82514</t>
+          <t>90393</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9535,32 +9535,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>66168</t>
+          <t>73313</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>55315</t>
+          <t>61115</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>77936</t>
+          <t>86816</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9570,32 +9570,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>135728</t>
+          <t>146790</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>116428</t>
+          <t>127650</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>157074</t>
+          <t>167673</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
@@ -9613,32 +9613,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18709</t>
+          <t>20769</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10921</t>
+          <t>11688</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29415</t>
+          <t>31695</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9648,32 +9648,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>25754</t>
+          <t>28668</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17778</t>
+          <t>20087</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35251</t>
+          <t>39636</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9683,32 +9683,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>44464</t>
+          <t>49437</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32825</t>
+          <t>37413</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57322</t>
+          <t>65492</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -9726,32 +9726,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16543</t>
+          <t>17710</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8912</t>
+          <t>9108</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30520</t>
+          <t>35371</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9761,32 +9761,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12919</t>
+          <t>14713</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7670</t>
+          <t>8844</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20970</t>
+          <t>24291</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9796,32 +9796,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>29461</t>
+          <t>32422</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19341</t>
+          <t>21832</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43423</t>
+          <t>48446</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -9839,17 +9839,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>242059</t>
+          <t>268134</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>242059</t>
+          <t>268134</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>242059</t>
+          <t>268134</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>199066</t>
+          <t>219483</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>199066</t>
+          <t>219483</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>199066</t>
+          <t>219483</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9909,17 +9909,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>441125</t>
+          <t>487617</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>441125</t>
+          <t>487617</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>441125</t>
+          <t>487617</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9956,32 +9956,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>518622</t>
+          <t>308687</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>341018</t>
+          <t>275360</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>773344</t>
+          <t>342178</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9991,32 +9991,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>209531</t>
+          <t>233038</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>174847</t>
+          <t>210398</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>232794</t>
+          <t>254550</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10026,32 +10026,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>728153</t>
+          <t>541724</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>544027</t>
+          <t>503153</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1122900</t>
+          <t>582121</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>
@@ -10069,32 +10069,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>294836</t>
+          <t>310554</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>166276</t>
+          <t>278281</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>389949</t>
+          <t>343950</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10104,32 +10104,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>230671</t>
+          <t>252889</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>187727</t>
+          <t>232485</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>254768</t>
+          <t>276022</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>525506</t>
+          <t>563442</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>337464</t>
+          <t>526048</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>625238</t>
+          <t>602877</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -10182,32 +10182,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>187308</t>
+          <t>217034</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>96607</t>
+          <t>189744</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>250234</t>
+          <t>248299</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10217,32 +10217,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>136594</t>
+          <t>153960</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>114467</t>
+          <t>133086</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>157517</t>
+          <t>174423</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10252,32 +10252,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>323902</t>
+          <t>370994</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>206100</t>
+          <t>337527</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>389524</t>
+          <t>408651</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -10295,32 +10295,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>112069</t>
+          <t>140792</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59349</t>
+          <t>114470</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>156512</t>
+          <t>169410</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10330,32 +10330,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>103149</t>
+          <t>80492</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>68074</t>
+          <t>66254</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>234541</t>
+          <t>95586</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10365,32 +10365,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>215218</t>
+          <t>221284</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>144368</t>
+          <t>190650</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>307670</t>
+          <t>253434</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -10408,17 +10408,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1112835</t>
+          <t>977066</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1112835</t>
+          <t>977066</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1112835</t>
+          <t>977066</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1792779</t>
+          <t>1697444</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1792779</t>
+          <t>1697444</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1792779</t>
+          <t>1697444</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
